--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.223375966444885</v>
+        <v>2.341060681244698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.204369530932377</v>
+        <v>1.82415215418548</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CdS2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2.255354631762668</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CdS2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.801327270492591</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CdS3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.319665035267825</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CdS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.516008256589908</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.341060681244698</v>
+        <v>1.223375966444885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,67 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.82415215418548</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2.255354631762668</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CdS2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1.801327270492591</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2.319665035267825</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CdS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1.516008256589908</v>
+        <v>1.203027132367621</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Gap (eV)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Error (eV)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,7 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.190501355433966</v>
+        <v>1.191270410545737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05297788398706858</v>
       </c>
     </row>
     <row r="3">
@@ -461,6 +469,9 @@
       </c>
       <c r="C3" t="n">
         <v>1.110128237447043</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01071939767468418</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Sb2Se3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
